--- a/profiles/ro-crate/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/ro-crate/profile-crate/ro-crate-metadata.xlsx
@@ -10,12 +10,12 @@
     <sheet sheetId="4" name="@type=Organization" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="@type=CreativeWork" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="@type=ResourceDescriptor" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="@type=DigitalFormat" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="@type=rdfs_Class" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="@type=rdf_Property" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="@type=PropertyValue" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="@type=DefinedTerm" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="@type=ItemList" state="visible" r:id="rId15"/>
+    <sheet sheetId="7" name="@type=rdfs_Class" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="@type=rdf_Property" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="@type=PropertyValue" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="@type=DefinedTerm" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="@type=ItemList" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="@type=DigitalFormat" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -249,12 +249,207 @@
     <t>"#conformanceIndicators"</t>
   </si>
   <si>
+    <t>prov:specializationOf</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>sh:minCount</t>
+  </si>
+  <si>
+    <t>sh:maxCount</t>
+  </si>
+  <si>
+    <t>#RO-Crate_Metadata_Descriptor</t>
+  </si>
+  <si>
+    <t>rdfs:Class</t>
+  </si>
+  <si>
+    <t>RO-Crate Metadadata Descriptor</t>
+  </si>
+  <si>
+    <t>"http://schema.org/CreativeWork"</t>
+  </si>
+  <si>
+    <t>An RO-Crate @graph must contain an entity of Type @CreativeWork which is known as the RO-Crate Metadata descriptor.</t>
+  </si>
+  <si>
+    <t>#Root_Data_Entity</t>
+  </si>
+  <si>
+    <t>Root Data Entity</t>
+  </si>
+  <si>
+    <t>"http://schema.org/Dataset"</t>
+  </si>
+  <si>
+    <t>The Root Data Entity for an RO-Crate. This is the main entity of the RO-Crate and is the one that is referenced by the RO-Crate Metadata Descriptor.</t>
+  </si>
+  <si>
+    <t>#class_CreativeWorkLicense</t>
+  </si>
+  <si>
+    <t>License (Creative Work)</t>
+  </si>
+  <si>
+    <t>A license included as a Creative Work - with at least a name and description</t>
+  </si>
+  <si>
+    <t>rdfs:label</t>
+  </si>
+  <si>
+    <t>domainIncludes</t>
+  </si>
+  <si>
+    <t>rangeIncludes</t>
+  </si>
+  <si>
+    <t>rdfs:comment</t>
+  </si>
+  <si>
+    <t>#RO-Crate_Metadata_Descriptor.id</t>
+  </si>
+  <si>
+    <t>rdf:Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The RO-Crate Metadata </t>
+  </si>
+  <si>
+    <t>"#RO-Crate_Metadata_Descriptor"</t>
+  </si>
+  <si>
+    <t>"#propertyValue_RO-Crate_Metadata_Descriptor.id"</t>
+  </si>
+  <si>
+    <t>#RO-Crate_Metadata_Descriptor.about</t>
+  </si>
+  <si>
+    <t>This property on the RO-Crate Metadata Descriptor references the Root Data Entity.</t>
+  </si>
+  <si>
+    <t>"#Root_Data_Entity"</t>
+  </si>
+  <si>
+    <t>"http://schema.org/about"</t>
+  </si>
+  <si>
+    <t>http://schema.org/name</t>
+  </si>
+  <si>
+    <t>"Text"</t>
+  </si>
+  <si>
+    <t>"http://schema.org/name"</t>
+  </si>
+  <si>
+    <t>SHOULD identify the dataset to humans well enough to disambiguate it from other RO-Crates</t>
+  </si>
+  <si>
+    <t>#prop_description_Dataset</t>
+  </si>
+  <si>
+    <t>"http://schema.org/description"</t>
+  </si>
+  <si>
+    <t>(In addition to the name) SHOULD further elaborate on the name to provide a summary of the context in which the dataset is important.</t>
+  </si>
+  <si>
+    <t>#prop_datePublished_Dataset</t>
+  </si>
+  <si>
+    <t>datePublished</t>
+  </si>
+  <si>
+    <t>"schema:Date"</t>
+  </si>
+  <si>
+    <t>"http://schema.org/datePubished"</t>
+  </si>
+  <si>
+    <t>MUST be a string in ISO 8601 date format and SHOULD be specified to at least the precision of a day, MAY be a timestamp down to the millisecond.</t>
+  </si>
+  <si>
+    <t>#prop_license_Dataset</t>
+  </si>
+  <si>
+    <t>["#class_CreativeWorkLicense", "schema:URL", "schema:Text"]</t>
+  </si>
+  <si>
+    <t>"http://schema.org/license"</t>
+  </si>
+  <si>
+    <t>SHOULD link to a Contextual Entity in the RO-Crate Metadata File with a name and description. MAY have a URI (eg for Creative Commons or Open Source licenses). MAY if necessary be a textual description of how the RO-Crate may be used</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>#propertyValue_RO-Crate_Metadata_Descriptor.id</t>
+  </si>
+  <si>
+    <t>PropertyValue</t>
+  </si>
+  <si>
+    <t>RO-Crate Metadadata Descriptor Identifier Constraint</t>
+  </si>
+  <si>
+    <t>Allowed identifier value constraint for RO-Crate Metadadata Descriptor.</t>
+  </si>
+  <si>
+    <t>ro-crate-metadata.json</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ro/mode</t>
+  </si>
+  <si>
+    <t>DefinedTerm</t>
+  </si>
+  <si>
+    <t>Editor Mode</t>
+  </si>
+  <si>
+    <t>Role indicating a resource is an editor configuration mode file.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ro/conformance-indicators</t>
+  </si>
+  <si>
+    <t>Role indicating a resource enumerates identifiers that are accepted as conformance indicators for the profile.</t>
+  </si>
+  <si>
+    <t>itemListElement</t>
+  </si>
+  <si>
+    <t>#conformanceIndicators</t>
+  </si>
+  <si>
+    <t>ItemList</t>
+  </si>
+  <si>
+    <t>Supported conformsTo identifiers</t>
+  </si>
+  <si>
+    <t>Canonical identifiers that indicate conformance to this profile.</t>
+  </si>
+  <si>
+    <t>"https://language-research-technology.github.io/ro-crate-masp/profiles/ro-crate/profile-crate/"</t>
+  </si>
+  <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Hypertext Markup Language</t>
+  </si>
+  <si>
     <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/1149</t>
   </si>
   <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
     <t>Markdown</t>
   </si>
   <si>
@@ -262,201 +457,6 @@
   </si>
   <si>
     <t>JSON Data Interchange Format</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/471</t>
-  </si>
-  <si>
-    <t>Hypertext Markup Language</t>
-  </si>
-  <si>
-    <t>prov:specializationOf</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>sh:minCount</t>
-  </si>
-  <si>
-    <t>sh:maxCount</t>
-  </si>
-  <si>
-    <t>#RO-Crate_Metadata_Descriptor</t>
-  </si>
-  <si>
-    <t>rdfs:Class</t>
-  </si>
-  <si>
-    <t>RO-Crate Metadadata Descriptor</t>
-  </si>
-  <si>
-    <t>"http://schema.org/CreativeWork"</t>
-  </si>
-  <si>
-    <t>An RO-Crate @graph must contain an entity of Type @CreativeWork which is known as the RO-Crate Metadata descriptor.</t>
-  </si>
-  <si>
-    <t>#Root_Data_Entity</t>
-  </si>
-  <si>
-    <t>Root Data Entity</t>
-  </si>
-  <si>
-    <t>"http://schema.org/Dataset"</t>
-  </si>
-  <si>
-    <t>The Root Data Entity for an RO-Crate. This is the main entity of the RO-Crate and is the one that is referenced by the RO-Crate Metadata Descriptor.</t>
-  </si>
-  <si>
-    <t>#class_CreativeWorkLicense</t>
-  </si>
-  <si>
-    <t>License (Creative Work)</t>
-  </si>
-  <si>
-    <t>A license included as a Creative Work - with at least a name and description</t>
-  </si>
-  <si>
-    <t>rdfs:label</t>
-  </si>
-  <si>
-    <t>domainIncludes</t>
-  </si>
-  <si>
-    <t>rangeIncludes</t>
-  </si>
-  <si>
-    <t>rdfs:comment</t>
-  </si>
-  <si>
-    <t>#RO-Crate_Metadata_Descriptor.id</t>
-  </si>
-  <si>
-    <t>rdf:Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The RO-Crate Metadata </t>
-  </si>
-  <si>
-    <t>"#RO-Crate_Metadata_Descriptor"</t>
-  </si>
-  <si>
-    <t>"#propertyValue_RO-Crate_Metadata_Descriptor.id"</t>
-  </si>
-  <si>
-    <t>#RO-Crate_Metadata_Descriptor.about</t>
-  </si>
-  <si>
-    <t>This property on the RO-Crate Metadata Descriptor references the Root Data Entity.</t>
-  </si>
-  <si>
-    <t>"#Root_Data_Entity"</t>
-  </si>
-  <si>
-    <t>"http://schema.org/about"</t>
-  </si>
-  <si>
-    <t>http://schema.org/name</t>
-  </si>
-  <si>
-    <t>"Text"</t>
-  </si>
-  <si>
-    <t>"http://schema.org/name"</t>
-  </si>
-  <si>
-    <t>SHOULD identify the dataset to humans well enough to disambiguate it from other RO-Crates</t>
-  </si>
-  <si>
-    <t>#prop_description_Dataset</t>
-  </si>
-  <si>
-    <t>"http://schema.org/description"</t>
-  </si>
-  <si>
-    <t>(In addition to the name) SHOULD further elaborate on the name to provide a summary of the context in which the dataset is important.</t>
-  </si>
-  <si>
-    <t>#prop_datePublished_Dataset</t>
-  </si>
-  <si>
-    <t>datePublished</t>
-  </si>
-  <si>
-    <t>"schema:Date"</t>
-  </si>
-  <si>
-    <t>"http://schema.org/datePubished"</t>
-  </si>
-  <si>
-    <t>MUST be a string in ISO 8601 date format and SHOULD be specified to at least the precision of a day, MAY be a timestamp down to the millisecond.</t>
-  </si>
-  <si>
-    <t>#prop_license_Dataset</t>
-  </si>
-  <si>
-    <t>["#class_CreativeWorkLicense", "schema:URL", "schema:Text"]</t>
-  </si>
-  <si>
-    <t>"http://schema.org/license"</t>
-  </si>
-  <si>
-    <t>SHOULD link to a Contextual Entity in the RO-Crate Metadata File with a name and description. MAY have a URI (eg for Creative Commons or Open Source licenses). MAY if necessary be a textual description of how the RO-Crate may be used</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>#propertyValue_RO-Crate_Metadata_Descriptor.id</t>
-  </si>
-  <si>
-    <t>PropertyValue</t>
-  </si>
-  <si>
-    <t>RO-Crate Metadadata Descriptor Identifier Constraint</t>
-  </si>
-  <si>
-    <t>Allowed identifier value constraint for RO-Crate Metadadata Descriptor.</t>
-  </si>
-  <si>
-    <t>ro-crate-metadata.json</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ro/mode</t>
-  </si>
-  <si>
-    <t>DefinedTerm</t>
-  </si>
-  <si>
-    <t>Editor Mode</t>
-  </si>
-  <si>
-    <t>Role indicating a resource is an editor configuration mode file.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ro/conformance-indicators</t>
-  </si>
-  <si>
-    <t>Role indicating a resource enumerates identifiers that are accepted as conformance indicators for the profile.</t>
-  </si>
-  <si>
-    <t>itemListElement</t>
-  </si>
-  <si>
-    <t>#conformanceIndicators</t>
-  </si>
-  <si>
-    <t>ItemList</t>
-  </si>
-  <si>
-    <t>Supported conformsTo identifiers</t>
-  </si>
-  <si>
-    <t>Canonical identifiers that indicate conformance to this profile.</t>
-  </si>
-  <si>
-    <t>"https://language-research-technology.github.io/ro-crate-masp/profiles/ro-crate/profile-crate/"</t>
   </si>
 </sst>
 </file>
@@ -944,66 +944,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1026,30 +966,30 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
         <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1080,23 +1020,81 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" t="s">
         <v>140</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>141</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" t="s">
         <v>142</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>143</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1445,64 +1443,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1520,16 +1460,16 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
         <v>8</v>
@@ -1537,19 +1477,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1560,16 +1500,16 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1578,24 +1518,24 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1604,7 +1544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1623,45 +1563,45 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1670,21 +1610,21 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1693,10 +1633,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J3" t="s">
         <v>25</v>
@@ -1704,118 +1644,178 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J4" t="s">
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J5" t="s">
         <v>8</v>
       </c>
       <c r="K5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K6" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I7" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>126</v>
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
